--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC506B33-24EE-44A8-8F92-2E562B62DCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023652E0-1912-4176-96AF-7D9D7B81B798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>資材コード</t>
   </si>
@@ -784,6 +784,16 @@
       <t>カナグ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GS4-15228-00</t>
+  </si>
+  <si>
+    <t>外壁金具12mm（25セット）</t>
+    <rPh sb="0" eb="4">
+      <t>ガイヘキカナグ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1196,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1917,6 +1927,17 @@
       </c>
       <c r="D64" s="6"/>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>177</v>
+      </c>
+      <c r="B65">
+        <v>2600040</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023652E0-1912-4176-96AF-7D9D7B81B798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD11A131-B188-4DC5-A720-AB35EE76EB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品名一覧" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>資材コード</t>
   </si>
@@ -792,6 +805,46 @@
     <t>外壁金具12mm（25セット）</t>
     <rPh sb="0" eb="4">
       <t>ガイヘキカナグ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GS4-17570-00</t>
+  </si>
+  <si>
+    <t>外壁受金具12mm（２５セット）</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヘキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カナグ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>8W002543</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ﾌﾚｰﾑｺﾃｲｶﾅｸﾞPC Q</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GS4-17572-00</t>
+  </si>
+  <si>
+    <t>外壁受金具12mm（50セット）</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヘキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カナグ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1206,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1819,123 +1872,156 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>159</v>
-      </c>
-      <c r="B56">
-        <v>2600002</v>
-      </c>
-      <c r="C56" t="s">
-        <v>160</v>
-      </c>
-      <c r="D56" s="6"/>
+    <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B56" s="2">
+        <v>4400451</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B57">
-        <v>2600005</v>
+        <v>2600002</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D57" s="6"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B58">
-        <v>2600020</v>
+        <v>2600005</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B59">
-        <v>2600050</v>
+        <v>2600020</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B60">
-        <v>2600041</v>
+        <v>2600050</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B61">
-        <v>2600042</v>
+        <v>2600041</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B62">
-        <v>2600047</v>
+        <v>2600042</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B63">
-        <v>2600049</v>
+        <v>2600047</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64">
+        <v>2600049</v>
+      </c>
+      <c r="C64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" s="6"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>168</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>2600048</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>176</v>
       </c>
-      <c r="D64" s="6"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="D65" s="6"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>177</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <v>2600040</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67">
+        <v>2600044</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>183</v>
+      </c>
+      <c r="B68">
+        <v>2600045</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD11A131-B188-4DC5-A720-AB35EE76EB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAD293E-8EBC-4639-BE69-FB65ED1BFD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>資材コード</t>
   </si>
@@ -128,43 +128,28 @@
     <t>配管固具ｱﾗｲﾊﾞ 8C813</t>
   </si>
   <si>
-    <t>4400813-50</t>
-  </si>
-  <si>
     <t>8C000814</t>
   </si>
   <si>
     <t>配管固定ｱﾗｲﾊﾞ 8C814</t>
   </si>
   <si>
-    <t>4400814-50</t>
-  </si>
-  <si>
     <t>8C000817</t>
   </si>
   <si>
     <t>配管固定ｱﾗｲﾊﾞ 8C817</t>
   </si>
   <si>
-    <t>4400817-50</t>
-  </si>
-  <si>
     <t>8C000844</t>
   </si>
   <si>
     <t>配管固定ｱﾗｲﾊﾞ 8C844</t>
   </si>
   <si>
-    <t>4400818-50</t>
-  </si>
-  <si>
     <t>8C000845</t>
   </si>
   <si>
     <t>配管固定ｱﾗｲﾊﾞ 8C845</t>
-  </si>
-  <si>
-    <t>4400819-50</t>
   </si>
   <si>
     <t>8C001063</t>
@@ -671,9 +656,6 @@
     <t>EB1-12563-00</t>
   </si>
   <si>
-    <t>HK3-01848-00</t>
-  </si>
-  <si>
     <t>GS4-15495-00</t>
   </si>
   <si>
@@ -727,22 +709,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鋼製大引陽束金物 防湿U=284</t>
-    <rPh sb="0" eb="2">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>オオヒキヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ツカカナモノ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ボウシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>外壁金具50セット</t>
     <rPh sb="0" eb="2">
       <t>ガイヘキ</t>
@@ -847,6 +813,25 @@
       <t>カナグ</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>鋼製大引用束金物 ベタ基礎</t>
+    <rPh sb="0" eb="2">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>オオヒキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ツカカナモノ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1275,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
@@ -1381,8 +1366,8 @@
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>31</v>
+      <c r="B11" s="2">
+        <v>4400813</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>30</v>
@@ -1390,638 +1375,634 @@
     </row>
     <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2">
+        <v>4400814</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4400817</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4400818</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4400819</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2">
         <v>4400292</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2">
         <v>4400898</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2">
         <v>4400067</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2">
         <v>4400145</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B48" s="2">
         <v>4400134</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B49" s="2">
         <v>4400146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B56" s="2">
         <v>4400451</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B57">
         <v>2600002</v>
       </c>
       <c r="C57" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D57" s="6"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B58">
         <v>2600005</v>
       </c>
       <c r="C58" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B59">
-        <v>2600020</v>
+        <v>2600002</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B60">
-        <v>2600050</v>
+        <v>2600041</v>
       </c>
       <c r="C60" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B61">
-        <v>2600041</v>
+        <v>2600042</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B62">
-        <v>2600042</v>
+        <v>2600047</v>
       </c>
       <c r="C62" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B63">
-        <v>2600047</v>
+        <v>2600049</v>
       </c>
       <c r="C63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B64">
-        <v>2600049</v>
+        <v>2600048</v>
       </c>
       <c r="C64" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B65">
-        <v>2600048</v>
-      </c>
-      <c r="C65" t="s">
+        <v>2600040</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66">
+        <v>2600044</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>176</v>
       </c>
-      <c r="D65" s="6"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="B67">
+        <v>2600045</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B66">
-        <v>2600040</v>
-      </c>
-      <c r="C66" s="6" t="s">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>2600020</v>
+      </c>
+      <c r="C68" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>179</v>
-      </c>
-      <c r="B67">
-        <v>2600044</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>183</v>
-      </c>
-      <c r="B68">
-        <v>2600045</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAD293E-8EBC-4639-BE69-FB65ED1BFD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EA5E67-AC9E-4A67-948A-71651A711503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="732" windowWidth="23040" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品名一覧" sheetId="1" r:id="rId1"/>
@@ -650,9 +650,6 @@
     <t>ﾂｶｶﾅﾓﾉ(Uｶﾞﾀ)H=186</t>
   </si>
   <si>
-    <t>HK3-01480-00</t>
-  </si>
-  <si>
     <t>EB1-12563-00</t>
   </si>
   <si>
@@ -832,6 +829,9 @@
       <t>キソ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HK3-01848-00</t>
   </si>
 </sst>
 </file>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B56" s="2">
         <v>4400451</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -1882,119 +1882,119 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B58">
         <v>2600005</v>
       </c>
       <c r="C58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B59">
         <v>2600002</v>
       </c>
       <c r="C59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B60">
         <v>2600041</v>
       </c>
       <c r="C60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B61">
         <v>2600042</v>
       </c>
       <c r="C61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B62">
         <v>2600047</v>
       </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B63">
         <v>2600049</v>
       </c>
       <c r="C63" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B64">
         <v>2600048</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B65">
         <v>2600040</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B66">
         <v>2600044</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B67">
         <v>2600045</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -2002,7 +2002,7 @@
         <v>2600020</v>
       </c>
       <c r="C68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EA5E67-AC9E-4A67-948A-71651A711503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520B422-7957-41A6-AE28-F957C2B5B907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="732" windowWidth="23040" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品名一覧" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t>資材コード</t>
   </si>
@@ -315,12 +315,6 @@
   </si>
   <si>
     <t>8Z000048</t>
-  </si>
-  <si>
-    <t>嵌合部品 S8W004858 H</t>
-  </si>
-  <si>
-    <t>4400485</t>
   </si>
   <si>
     <t>8Z000049</t>
@@ -832,6 +826,49 @@
   </si>
   <si>
     <t>HK3-01848-00</t>
+  </si>
+  <si>
+    <t>8Z000050</t>
+  </si>
+  <si>
+    <t>吊り具11N・12Nセット</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>グ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>8W002529</t>
+  </si>
+  <si>
+    <t>フレーム固定金具PC ツヤメキ用</t>
+    <rPh sb="4" eb="8">
+      <t>コテイカナグ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>吊り具11Nセット</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>グ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>8W002534</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ﾌﾚｰﾑ固定金具PC B 8W002534 HMD64072B</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1260,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
@@ -1623,386 +1660,419 @@
         <v>4400898</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>94</v>
+      <c r="B35" s="2">
+        <v>4400066</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B36" s="2">
         <v>4400067</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B45" s="2">
         <v>4400145</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B48" s="2">
         <v>4400134</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2">
         <v>4400146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B56" s="2">
         <v>4400451</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>154</v>
-      </c>
-      <c r="B57">
-        <v>2600002</v>
-      </c>
-      <c r="C57" t="s">
-        <v>155</v>
-      </c>
-      <c r="D57" s="6"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B57" s="2">
+        <v>4400441</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58">
+        <v>4400068</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B58">
-        <v>2600005</v>
-      </c>
-      <c r="C58" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="B59">
-        <v>2600002</v>
-      </c>
-      <c r="C59" t="s">
-        <v>163</v>
-      </c>
-      <c r="D59" s="6"/>
+        <v>4400432</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B60">
-        <v>2600041</v>
+        <v>2600002</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B61">
-        <v>2600042</v>
+        <v>2600005</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B62">
-        <v>2600047</v>
+        <v>2600002</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B63">
-        <v>2600049</v>
+        <v>2600041</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B64">
+        <v>2600042</v>
+      </c>
+      <c r="C64" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" s="6"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65">
+        <v>2600047</v>
+      </c>
+      <c r="C65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" s="6"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66">
+        <v>2600049</v>
+      </c>
+      <c r="C66" t="s">
+        <v>165</v>
+      </c>
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67">
         <v>2600048</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68">
+        <v>2600040</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D64" s="6"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>169</v>
       </c>
-      <c r="B65">
-        <v>2600040</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="B69">
+        <v>2600044</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>171</v>
-      </c>
-      <c r="B66">
-        <v>2600044</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70">
+        <v>2600045</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>2600020</v>
+      </c>
+      <c r="C71" t="s">
         <v>175</v>
-      </c>
-      <c r="B67">
-        <v>2600045</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B68">
-        <v>2600020</v>
-      </c>
-      <c r="C68" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520B422-7957-41A6-AE28-F957C2B5B907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A360C43D-4E49-4525-A2BE-6DA269464BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>資材コード</t>
   </si>
@@ -869,6 +869,17 @@
   </si>
   <si>
     <t>ﾌﾚｰﾑ固定金具PC B 8W002534 HMD64072B</t>
+  </si>
+  <si>
+    <t>8W004849</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フレーム固定金具</t>
+    <rPh sb="4" eb="8">
+      <t>コテイカナグ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1281,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1938,140 +1949,151 @@
         <v>180</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B60">
-        <v>2600002</v>
-      </c>
-      <c r="C60" t="s">
-        <v>153</v>
-      </c>
-      <c r="D60" s="6"/>
+    <row r="60" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" s="2">
+        <v>4400484</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B61">
-        <v>2600005</v>
+        <v>2600002</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B62">
-        <v>2600002</v>
+        <v>2600005</v>
       </c>
       <c r="C62" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B63">
-        <v>2600041</v>
+        <v>2600002</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B64">
-        <v>2600042</v>
+        <v>2600041</v>
       </c>
       <c r="C64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B65">
-        <v>2600047</v>
+        <v>2600042</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B66">
-        <v>2600049</v>
+        <v>2600047</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D66" s="6"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B67">
-        <v>2600048</v>
+        <v>2600049</v>
       </c>
       <c r="C67" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D67" s="6"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B68">
-        <v>2600040</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>168</v>
-      </c>
+        <v>2600048</v>
+      </c>
+      <c r="C68" t="s">
+        <v>166</v>
+      </c>
+      <c r="D68" s="6"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B69">
-        <v>2600044</v>
+        <v>2600040</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70">
+        <v>2600044</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>173</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>2600045</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C71" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B71">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B72">
         <v>2600020</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C72" t="s">
         <v>175</v>
       </c>
     </row>

--- a/hinmei_master.xlsx
+++ b/hinmei_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A360C43D-4E49-4525-A2BE-6DA269464BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37967F9F-6301-4A70-8D6D-A13C84EAB429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品名一覧" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>資材コード</t>
   </si>
@@ -321,12 +321,6 @@
   </si>
   <si>
     <t>8W004803</t>
-  </si>
-  <si>
-    <t>L-CKU-1AR (K4803)</t>
-  </si>
-  <si>
-    <t>4300803</t>
   </si>
   <si>
     <t>8W002448</t>
@@ -878,6 +872,13 @@
     <t>フレーム固定金具</t>
     <rPh sb="4" eb="8">
       <t>コテイカナグ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>天井繋ぎアングル</t>
+    <rPh sb="0" eb="3">
+      <t>テンジョウツナ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1308,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
@@ -1671,7 +1672,7 @@
         <v>4400898</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
@@ -1682,7 +1683,7 @@
         <v>4400066</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
@@ -1693,400 +1694,400 @@
         <v>4400067</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>96</v>
+      <c r="B37" s="2">
+        <v>4400302</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2">
         <v>4400145</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2">
         <v>4400134</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2">
         <v>4400146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B56" s="2">
         <v>4400451</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B57" s="2">
         <v>4400441</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B58">
         <v>4400068</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B59">
         <v>4400432</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B60" s="2">
         <v>4400484</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B61">
         <v>2600002</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B62">
         <v>2600005</v>
       </c>
       <c r="C62" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B63">
         <v>2600002</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B64">
         <v>2600041</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B65">
         <v>2600042</v>
       </c>
       <c r="C65" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B66">
         <v>2600047</v>
       </c>
       <c r="C66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D66" s="6"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B67">
         <v>2600049</v>
       </c>
       <c r="C67" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D67" s="6"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B68">
         <v>2600048</v>
       </c>
       <c r="C68" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D68" s="6"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B69">
         <v>2600040</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B70">
         <v>2600044</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B71">
         <v>2600045</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -2094,7 +2095,7 @@
         <v>2600020</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
